--- a/marketing/TCG-Express-print-quote-comparison.xlsx
+++ b/marketing/TCG-Express-print-quote-comparison.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 품목별 비교" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 결정 요약" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 미회신 추적" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. 전체 접촉 현황" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 8-29 갱신" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 품목별 비교" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 결정 요약" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 미회신 추적" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,7 +59,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +84,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDF1D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -136,6 +143,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -501,6 +514,1232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>접촉한 업체 전부 — 한 곳도 빠지지 않게</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29 기준. 회신이 없는 곳도 전부 남깁니다. 비교표에서 사라지면 '연락 안 한 것'처럼 보이기 때문입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>업체</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>연락처</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>최초 접촉</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>발송</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>최종 회신</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>다음 조치</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Fatty Print</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>cso1@fattyprint.com.sg (Ginnie)
+Tel 6100 1266</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>9통</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>8/29 09:33</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>활발</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>전단 익스프레스 $219 — 월 11시 전 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Lim Sign</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>sales@limsign.com.sg (Daphne)
+Tel 6336 0443 · WA 8030 1235</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>4통</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>**8/29 11:57**</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>활발</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>배지 랜야드·변수데이터 확인 회신 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Kiasu Print</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>sales@kiasuprint.com</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>5통</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>8/26 17:08</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>회신 후 정지</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>배너 하드웨어 확인 회신 대기 — 발주 예정처</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Raffles Tag</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>sales@rafflestag.sg (Ahmad)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>5통</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>8/26 22:57</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>**3일 무응답**</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>8/29 리마인드 발송함. 월요일까지 무응답 시 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>CustomPrint</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>sales@customprint.com.sg (Loghini)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>8/19 이전</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>6통</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>**8/19 16:07**</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>**10일 무응답**</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>8/29 정정+재요청 발송함. 견적 9/18 만료</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>**알리바바 Printing**</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>info@alibabaprinting.sg
+**Tel/WhatsApp 9146 1431**
+3 Ang Mo Kio St 62, #02-02</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>**8/26**</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>**4통**</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>**없음**</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>**3일 무응답**</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>★ 메일이 안 통함. 월요일 오전 WhatsApp 9146 1431로 직접 연락 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>SG E Print</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>sgeprintsales@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>3통</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>8/27 14:05</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>회신함</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>전단만 가능 + 온라인 등록 필수 → 실효성 낮음</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Express Print</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>info@expressprint.com.sg</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>3통</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>무응답</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Printing.com.sg</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>enquiry@printing.com.sg</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>3통</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>티켓 자동응답만</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>무응답</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>티켓 2225·2239 열림. 실견적 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>The Copy Boy</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>sales@thecopyboy.com</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>1통</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>무응답</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>XPrint</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>xprint@xprint.com.sg</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>1통</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>무응답</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Ace Print</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>info@aceprint.com.sg</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>1통</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>**메일 반송**</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>주소 없음</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>제외 — 550 No such user</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>GoGoPrint</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>support@gogoprint.sg</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>1통</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>**메일 반송**</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>주소 없음</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>제외 — 주소 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>LY Acme (중국)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>info@lyacme.com (Honglei)
+acmegraphic.com</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>8/21</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>6통</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>8/28 11:02</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>활발</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>데칼 3–5년 USD 7,133 CIF. 샘플가 전도 여부 질의 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Dekawrap (중국)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>betty@dekawrap.com (Betty)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>8/21</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>6통</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>8/28 14:00</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>활발</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>블록 사양 재견적 미도착 — 본문 금액 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>VWrap.sg</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>vwrap.sg@gmail.com (Goh Yik Khoon)
+Mobile 9672 1585</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>8/21</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>5통</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>8/27 10:15</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>2일 무응답</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>구 사양 단가만 ($6/$11 psf). 신규 물량 재견적 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>알리바바 Printing — 왜 아직 견적이 없는가</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>8월 26일 첫 연락 이후 4통을 보냈고 한 번도 회신이 없습니다. 반송(bounce)은 없었으므로 주소는 유효하고, 메일이 도달했으나 읽히지 않거나 필터에 걸린 것입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>초기 메일들의 아트워크 링크가 google.com/url 로 재작성돼 있었습니다 — Dekawrap·VWrap·Fatty Print가 모두 '링크가 안 열린다'고 회신한 그 문제입니다. 스팸 판정 요인이 됐을 가능성이 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>8/29에 프로토콜 없는 링크로 전체 패키지 RFQ를 재발송했습니다. 여기에도 응답이 없으면 메일 채널은 죽은 것으로 봐야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>웹사이트에 전화 겸 WhatsApp 번호가 있습니다: 9146 1431 (Link @ AMK, 3 Ang Mo Kio Street 62, #02-02). 전단이 이 회사의 주력 품목이므로, 월요일 오전에 한 통 걸어볼 가치가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>다만 전단은 이미 Fatty Print 익스프레스가 유일하게 9/3 납기를 맞출 수 있는 옵션이고 마감이 월요일 11시입니다. 알리바바가 더 싸게 나오더라도 납기를 못 맞추면 의미가 없습니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>8월 29일(토) 갱신 — Lim Sign 회신 도착, 배너 결정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Lim Sign이 전 품목에 답했습니다. 배너는 결론이 났고, 배지는 순위가 바뀌었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>업체</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>납기</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>롤업 배너 4개</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Kiasu Print</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>$432 ($108/개)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>3–4영업일</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>★ 확정 권장</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>무광 서면 확인. 런칭 주 납품 가능. GST 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Lim Sign</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>$512 ($128/개, 무광)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>**9월 2주차 입고**</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>탈락</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>무광은 가능하나 재고 없음 — 런칭일에 못 세움. 가격도 더 비쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Fatty / Raffles</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>미회신</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A5 전단 2,000장</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Fatty Print</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>$179 / **$219 익스프레스**</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2영업일(익스프레스)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>★ 확정 권장</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>8/31 11시까지 아트워크 → 9/2 오후 납품</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Lim Sign</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>$328</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>3영업일</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>탈락</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Fatty 대비 $109 비쌈</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Kiasu Print</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>$550</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>2–4영업일</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>탈락</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>3배</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>프로모터 배지 20세트</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Lim Sign</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>$3.50/장 = **$70**</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>5영업일</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>★ 확인 중</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>최저가. 랜야드·변수데이터 포함 여부 확인 요청 발송함</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Fatty Print</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>15세트 $152 (랜야드 포함)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>4–5영업일</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>비교 열세</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>세트당 $10.13. 20세트 재견적 미도착</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Raffles Tag</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>30장 $1.58/장 (카드만)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>7영업일</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>비교 불가</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>랜야드 가격을 3일째 본문에 안 줌</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>티셔츠 50장</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>CustomPrint</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>100장 $12.90/장</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>15영업일</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>막힘</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>50장 가격 없음 · 뒷면 최대 A3(디자인 초과) · 9/10 납기 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Lim Sign / Kiasu</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>취급 안 함</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>불가</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>차량 데칼</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Lim Sign</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>24ft $650 / 14ft $480 / 밴측면 $450 (공급)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>보류</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>설치 별도 $450/$350/$280. 3–5년/5–7년 구분 미제시 — 질의함</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>LY Acme</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>3–5년 USD 7,133 CIF</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>생산15–17 + 해상25–35영업일</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>최저가·납기 초과</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>10월 중순 도착. 항만비·통관·GST 별도</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Dekawrap / VWrap</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>금액 없음</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>미도착</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>월요일 발주 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>전단  Fatty Print 익스프레스 $219 + GST  →  8/31 오전 11시 전 확정 (하드 데드라인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>배너  Kiasu Print $432, GST 없음  →  알루미늄 카세트·캐리백 포함 여부만 확인 후 발주</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>배지  Lim Sign $70 유력  →  랜야드·변수데이터 포함 여부 회신 대기. 9/4 아트워크 확정 후 발주하면 9/10 납품 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>티셔츠  결정 필요 — A3로 축소 / 런칭 후로 연기 / 다른 업체</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>데칼  9월 중하순. 급하지 않음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1144,7 +2383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1414,7 +2653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
